--- a/data/excel/person.xlsx
+++ b/data/excel/person.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H176"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -846,6 +846,5254 @@
         <v>1</v>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>任弼时</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="n">
+        <v>1904</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1950</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>湖南湘阴</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>中共第一代中央领导集体成员，长期主持中央书记处工作，被誉为党的骆驼。</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>陈云</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="n">
+        <v>1905</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1995</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>上海青浦</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>中共第一代、第二代中央领导集体重要成员，长期主管全国经济工作，中央纪委第一书记。</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>邓颖超</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="n">
+        <v>1904</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1992</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>河南光山</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>无产阶级革命家、政治家，中国妇女运动的先驱，曾任全国政协主席。</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>李先念</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="n">
+        <v>1909</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1992</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>湖北红安</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>无产阶级革命家，曾任国务院副总理兼财政部长、中华人民共和国主席。</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>杨尚昆</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="n">
+        <v>1907</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1998</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>四川潼南</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>无产阶级革命家，长期任中共中央办公厅主任，后任中华人民共和国主席。</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>彭真</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="n">
+        <v>1902</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1997</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>山西曲沃</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>无产阶级革命家、法学家，新中国社会主义法制的主要奠基人之一，曾任全国人大常委会委员长。</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>叶剑英</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="n">
+        <v>1897</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1986</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>广东梅县</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>中国人民解放军创建人之一，中华人民共和国元帅，曾任全国人大常委会委员长。</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>胡耀邦</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="n">
+        <v>1915</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1989</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>湖南浏阳</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>曾任中共中央总书记，在推动拨乱反正和平反冤假错案中作出重要贡献。</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>华国锋</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="n">
+        <v>1921</v>
+      </c>
+      <c r="D22" t="n">
+        <v>2008</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>山西交城</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>曾任中共中央主席、国务院总理、中央军委主席。</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>江泽民</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="n">
+        <v>1926</v>
+      </c>
+      <c r="D23" t="n">
+        <v>2022</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>江苏扬州</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>中共第三代中央领导集体的核心，「三个代表」重要思想的主要创立者。</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H23" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>李鹏</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="n">
+        <v>1928</v>
+      </c>
+      <c r="D24" t="n">
+        <v>2019</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>曾任国务院总理、全国人大常委会委员长。</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>朱镕基</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr"/>
+      <c r="C25" t="n">
+        <v>1928</v>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>湖南长沙</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>曾任国务院副总理、国务院总理，主持社会主义市场经济体制改革的一系列重大举措。</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H25" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>胡锦涛</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="n">
+        <v>1942</v>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>安徽绩溪</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>曾任中共中央总书记、国家主席、中央军委主席，科学发展观的主要创立者。</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H26" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>温家宝</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr"/>
+      <c r="C27" t="n">
+        <v>1942</v>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>天津</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>曾任国务院总理。</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H27" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>习近平</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr"/>
+      <c r="C28" t="n">
+        <v>1953</v>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>陕西富平</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>中共中央总书记、国家主席、中央军委主席，习近平新时代中国特色社会主义思想的主要创立者。</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H28" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>李克强</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr"/>
+      <c r="C29" t="n">
+        <v>1955</v>
+      </c>
+      <c r="D29" t="n">
+        <v>2023</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>安徽定远</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>曾任国务院总理。</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H29" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>瞿秋白</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr"/>
+      <c r="C30" t="n">
+        <v>1899</v>
+      </c>
+      <c r="D30" t="n">
+        <v>1935</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>江苏常州</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>中共早期主要领导人之一，中国革命文学事业的重要奠基者，1935 年在福建长汀就义。</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H30" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>蔡和森</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr"/>
+      <c r="C31" t="n">
+        <v>1895</v>
+      </c>
+      <c r="D31" t="n">
+        <v>1931</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>湖南湘乡</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>中共早期重要领导人之一，最早明确提出成立中国共产党的党员之一。</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H31" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>向警予</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr"/>
+      <c r="C32" t="n">
+        <v>1895</v>
+      </c>
+      <c r="D32" t="n">
+        <v>1928</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>湖南溆浦</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>中共早期妇女运动领导人，中共第一位女中央委员。</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H32" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>邓中夏</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr"/>
+      <c r="C33" t="n">
+        <v>1894</v>
+      </c>
+      <c r="D33" t="n">
+        <v>1933</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>湖南宜章</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>中国工人运动的著名活动家，省港大罢工的主要领导人之一。</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H33" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>张太雷</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr"/>
+      <c r="C34" t="n">
+        <v>1898</v>
+      </c>
+      <c r="D34" t="n">
+        <v>1927</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>江苏常州</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>中共早期重要领导人之一，广州起义主要领导人，在起义中牺牲。</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H34" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>恽代英</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr"/>
+      <c r="C35" t="n">
+        <v>1895</v>
+      </c>
+      <c r="D35" t="n">
+        <v>1931</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>湖北武昌</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>中共早期青年运动领导人，黄埔军校政治教官。</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H35" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>王尽美</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr"/>
+      <c r="C36" t="n">
+        <v>1898</v>
+      </c>
+      <c r="D36" t="n">
+        <v>1925</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>山东莒县</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>中共一大代表，山东党组织的创始人之一。</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H36" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>邓恩铭</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr"/>
+      <c r="C37" t="n">
+        <v>1901</v>
+      </c>
+      <c r="D37" t="n">
+        <v>1931</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>贵州荔波</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>中共一大代表，山东党组织创始人之一，中共一大代表中唯一的少数民族代表。</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H37" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>何叔衡</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr"/>
+      <c r="C38" t="n">
+        <v>1876</v>
+      </c>
+      <c r="D38" t="n">
+        <v>1935</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>湖南宁乡</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>中共一大代表，年龄最长的一大代表，1935 年在福建长汀突围时牺牲。</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H38" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>陈潭秋</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr"/>
+      <c r="C39" t="n">
+        <v>1896</v>
+      </c>
+      <c r="D39" t="n">
+        <v>1943</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>湖北黄冈</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>中共一大代表，1943 年在新疆迪化被军阀杀害。</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H39" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>包惠僧</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr"/>
+      <c r="C40" t="n">
+        <v>1894</v>
+      </c>
+      <c r="D40" t="n">
+        <v>1979</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>湖北黄冈</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>中共一大出席者，受陈独秀指派参加大会。</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H40" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>刘仁静</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr"/>
+      <c r="C41" t="n">
+        <v>1902</v>
+      </c>
+      <c r="D41" t="n">
+        <v>1987</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>湖北应城</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>中共一大代表。</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H41" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>李汉俊</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr"/>
+      <c r="C42" t="n">
+        <v>1890</v>
+      </c>
+      <c r="D42" t="n">
+        <v>1927</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>湖北潜江</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>中共一大代表，上海共产主义小组成员，一大会址即其兄寓所。</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H42" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>毛泽民</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr"/>
+      <c r="C43" t="n">
+        <v>1896</v>
+      </c>
+      <c r="D43" t="n">
+        <v>1943</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>湖南湘潭</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>中共早期经济工作领导人，1943 年在新疆迪化被军阀杀害。</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H43" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>王荷波</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr"/>
+      <c r="C44" t="n">
+        <v>1882</v>
+      </c>
+      <c r="D44" t="n">
+        <v>1927</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>福建福州</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>中国工人运动先驱，中共首任中央监察委员会主席。</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H44" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>方志敏</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr"/>
+      <c r="C45" t="n">
+        <v>1899</v>
+      </c>
+      <c r="D45" t="n">
+        <v>1935</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>江西弋阳</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>赣东北革命根据地和红十军的创建人，狱中写下《可爱的中国》，1935 年在南昌就义。</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H45" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>刘志丹</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr"/>
+      <c r="C46" t="n">
+        <v>1903</v>
+      </c>
+      <c r="D46" t="n">
+        <v>1936</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>陕西保安</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>陕甘边革命根据地的主要创建人之一，1936 年在东征作战中牺牲。</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H46" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>谢子长</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr"/>
+      <c r="C47" t="n">
+        <v>1897</v>
+      </c>
+      <c r="D47" t="n">
+        <v>1935</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>陕西安定</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>陕北红军和苏区创建人之一。</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H47" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>彭湃</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr"/>
+      <c r="C48" t="n">
+        <v>1896</v>
+      </c>
+      <c r="D48" t="n">
+        <v>1929</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>广东海丰</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>中国农民运动的先驱，海陆丰农民运动和苏维埃政权的主要领导人。</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H48" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>赵世炎</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr"/>
+      <c r="C49" t="n">
+        <v>1901</v>
+      </c>
+      <c r="D49" t="n">
+        <v>1927</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>四川酉阳</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>中共早期工人运动领导人，上海三次武装起义的主要领导人之一。</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H49" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>陈延年</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr"/>
+      <c r="C50" t="n">
+        <v>1898</v>
+      </c>
+      <c r="D50" t="n">
+        <v>1927</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>安徽怀宁</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>中共早期领导人，中共江浙区委书记，1927 年在上海就义。</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H50" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>夏明翰</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr"/>
+      <c r="C51" t="n">
+        <v>1900</v>
+      </c>
+      <c r="D51" t="n">
+        <v>1928</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>湖南衡阳</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>革命烈士，就义前写下「砍头不要紧，只要主义真」的就义诗。</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H51" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>杨靖宇</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr"/>
+      <c r="C52" t="n">
+        <v>1905</v>
+      </c>
+      <c r="D52" t="n">
+        <v>1940</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>河南确山</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>东北抗日联军主要创建人和领导人之一，1940 年在吉林濛江壮烈殉国。</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H52" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>赵一曼</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr"/>
+      <c r="C53" t="n">
+        <v>1905</v>
+      </c>
+      <c r="D53" t="n">
+        <v>1936</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>四川宜宾</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>东北抗日联军女指挥员，1936 年在黑龙江珠河就义。</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H53" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>左权</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr"/>
+      <c r="C54" t="n">
+        <v>1905</v>
+      </c>
+      <c r="D54" t="n">
+        <v>1942</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>湖南醴陵</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>八路军副参谋长，1942 年在山西辽县指挥反「扫荡」时牺牲。</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H54" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>彭雪枫</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr"/>
+      <c r="C55" t="n">
+        <v>1907</v>
+      </c>
+      <c r="D55" t="n">
+        <v>1944</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>河南镇平</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>新四军第四师师长兼政治委员，1944 年在河南夏邑作战牺牲。</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H55" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>叶挺</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr"/>
+      <c r="C56" t="n">
+        <v>1896</v>
+      </c>
+      <c r="D56" t="n">
+        <v>1946</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>广东惠阳</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>北伐名将，南昌起义前敌总指挥，新四军首任军长，1946 年因飞机失事遇难。</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H56" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>董存瑞</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr"/>
+      <c r="C57" t="n">
+        <v>1929</v>
+      </c>
+      <c r="D57" t="n">
+        <v>1948</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>河北怀来</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>中国人民解放军战斗英雄，1948 年在隆化战斗中舍身炸碉堡牺牲。</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H57" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>黄继光</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr"/>
+      <c r="C58" t="n">
+        <v>1931</v>
+      </c>
+      <c r="D58" t="n">
+        <v>1952</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>四川中江</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>中国人民志愿军特级英雄，1952 年在上甘岭战役中舍身堵枪眼牺牲。</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H58" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>邱少云</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr"/>
+      <c r="C59" t="n">
+        <v>1926</v>
+      </c>
+      <c r="D59" t="n">
+        <v>1952</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>四川铜梁</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>中国人民志愿军一级英雄，1952 年潜伏作战中被烈火烧身岿然不动壮烈牺牲。</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H59" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>雷锋</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr"/>
+      <c r="C60" t="n">
+        <v>1940</v>
+      </c>
+      <c r="D60" t="n">
+        <v>1962</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>湖南望城</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>中国人民解放军战士，全心全意为人民服务的楷模，毛泽东为其题词「向雷锋同志学习」。</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H60" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>焦裕禄</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr"/>
+      <c r="C61" t="n">
+        <v>1922</v>
+      </c>
+      <c r="D61" t="n">
+        <v>1964</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>山东淄博</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>河南兰考县委书记，带领群众治理风沙、内涝、盐碱，是县委书记的榜样。</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H61" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>王进喜</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>铁人</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>1923</v>
+      </c>
+      <c r="D62" t="n">
+        <v>1970</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>甘肃玉门</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>大庆石油会战中的钻井队长，被誉为「铁人」，工业战线的英雄模范。</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H62" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>孔繁森</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr"/>
+      <c r="C63" t="n">
+        <v>1944</v>
+      </c>
+      <c r="D63" t="n">
+        <v>1994</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>山东聊城</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>两次进藏工作的领导干部，殉职于阿里地区，党的优秀领导干部楷模。</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H63" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>谷文昌</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr"/>
+      <c r="C64" t="n">
+        <v>1915</v>
+      </c>
+      <c r="D64" t="n">
+        <v>1981</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>河南林县</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>福建东山县委书记，带领群众防风固沙、造林治理，「不带私心搞革命」的楷模。</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H64" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>白求恩</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>诺尔曼·白求恩</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>1890</v>
+      </c>
+      <c r="D65" t="n">
+        <v>1939</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>加拿大安大略</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>加拿大共产党员、医生，来华支援抗战并殉职，毛泽东为此写下《纪念白求恩》。</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H65" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>林彪</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr"/>
+      <c r="C66" t="n">
+        <v>1907</v>
+      </c>
+      <c r="D66" t="n">
+        <v>1971</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>湖北黄冈</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>中华人民共和国元帅，解放战争时期第四野战军司令员，后策动反革命政变，出逃途中坠机身亡。</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H66" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>刘伯承</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr"/>
+      <c r="C67" t="n">
+        <v>1892</v>
+      </c>
+      <c r="D67" t="n">
+        <v>1986</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>四川开县</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>中华人民共和国元帅，与邓小平共同指挥晋冀鲁豫野战军挺进大别山。</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H67" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>罗荣桓</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr"/>
+      <c r="C68" t="n">
+        <v>1902</v>
+      </c>
+      <c r="D68" t="n">
+        <v>1963</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>湖南衡山</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>中华人民共和国元帅，人民军队政治工作的杰出领导人。</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H68" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>徐向前</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr"/>
+      <c r="C69" t="n">
+        <v>1901</v>
+      </c>
+      <c r="D69" t="n">
+        <v>1990</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>山西五台</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>中华人民共和国元帅，红四方面军总指挥。</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H69" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>聂荣臻</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr"/>
+      <c r="C70" t="n">
+        <v>1899</v>
+      </c>
+      <c r="D70" t="n">
+        <v>1992</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>四川江津</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>中华人民共和国元帅，晋察冀根据地创建人，新中国国防科技事业的主要奠基人之一。</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H70" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>粟裕</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr"/>
+      <c r="C71" t="n">
+        <v>1907</v>
+      </c>
+      <c r="D71" t="n">
+        <v>1984</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>湖南会同</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>中国人民解放军大将，华东野战军主要指挥员，指挥苏中战役、孟良崮战役、淮海战役等。</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H71" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>徐海东</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr"/>
+      <c r="C72" t="n">
+        <v>1900</v>
+      </c>
+      <c r="D72" t="n">
+        <v>1970</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>湖北黄陂</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>中国人民解放军大将，红二十五军主要领导人。</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H72" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>黄克诚</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr"/>
+      <c r="C73" t="n">
+        <v>1902</v>
+      </c>
+      <c r="D73" t="n">
+        <v>1986</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>湖南永兴</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>中国人民解放军大将，曾任中央军委秘书长、中央纪委常务书记。</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H73" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>陈赓</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr"/>
+      <c r="C74" t="n">
+        <v>1903</v>
+      </c>
+      <c r="D74" t="n">
+        <v>1961</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>湖南湘乡</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>中国人民解放军大将，哈尔滨军事工程学院首任院长。</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H74" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>谭政</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr"/>
+      <c r="C75" t="n">
+        <v>1906</v>
+      </c>
+      <c r="D75" t="n">
+        <v>1988</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>湖南湘乡</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>中国人民解放军大将，人民军队政治工作领导人之一。</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H75" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>萧劲光</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr"/>
+      <c r="C76" t="n">
+        <v>1903</v>
+      </c>
+      <c r="D76" t="n">
+        <v>1989</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>湖南长沙</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>中国人民解放军大将，人民海军首任司令员。</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H76" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>张云逸</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr"/>
+      <c r="C77" t="n">
+        <v>1892</v>
+      </c>
+      <c r="D77" t="n">
+        <v>1974</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>广东文昌</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>中国人民解放军大将，百色起义领导人之一。</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H77" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>罗瑞卿</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr"/>
+      <c r="C78" t="n">
+        <v>1906</v>
+      </c>
+      <c r="D78" t="n">
+        <v>1978</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>四川南充</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>中国人民解放军大将，新中国首任公安部部长。</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H78" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>王树声</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr"/>
+      <c r="C79" t="n">
+        <v>1905</v>
+      </c>
+      <c r="D79" t="n">
+        <v>1974</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>湖北麻城</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>中国人民解放军大将，鄂豫皖苏区创建人之一。</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H79" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>许光达</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr"/>
+      <c r="C80" t="n">
+        <v>1908</v>
+      </c>
+      <c r="D80" t="n">
+        <v>1969</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>湖南长沙</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>中国人民解放军大将，人民装甲兵首任司令员。</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H80" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>宋任穷</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr"/>
+      <c r="C81" t="n">
+        <v>1909</v>
+      </c>
+      <c r="D81" t="n">
+        <v>2005</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>湖南浏阳</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>中国人民解放军上将，曾任中共中央组织部部长。</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H81" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>王震</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr"/>
+      <c r="C82" t="n">
+        <v>1908</v>
+      </c>
+      <c r="D82" t="n">
+        <v>1993</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>湖南浏阳</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>中国人民解放军上将，三五九旅旅长，南泥湾大生产运动的组织者，后任国家副主席。</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H82" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>杨得志</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr"/>
+      <c r="C83" t="n">
+        <v>1911</v>
+      </c>
+      <c r="D83" t="n">
+        <v>1994</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>湖南醴陵</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>中国人民解放军上将，强渡大渡河先遣团团长，曾任人民解放军总参谋长。</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H83" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>许世友</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr"/>
+      <c r="C84" t="n">
+        <v>1905</v>
+      </c>
+      <c r="D84" t="n">
+        <v>1985</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>河南新县</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>中国人民解放军上将，济南战役、对越自卫反击战东线指挥员。</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H84" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>叶飞</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr"/>
+      <c r="C85" t="n">
+        <v>1914</v>
+      </c>
+      <c r="D85" t="n">
+        <v>1999</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>福建南安</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>中国人民解放军上将，曾任福建省委第一书记、海军司令员。</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H85" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>韦国清</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr"/>
+      <c r="C86" t="n">
+        <v>1913</v>
+      </c>
+      <c r="D86" t="n">
+        <v>1989</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>广西东兰</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>中国人民解放军上将，曾任中共中央军委总政治部主任。</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H86" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>刘华清</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr"/>
+      <c r="C87" t="n">
+        <v>1916</v>
+      </c>
+      <c r="D87" t="n">
+        <v>2011</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>湖北大悟</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>中国人民解放军上将，人民海军现代化建设的重要推动者。</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H87" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>孙中山</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>中山先生/孙文</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>1866</v>
+      </c>
+      <c r="D88" t="n">
+        <v>1925</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>广东香山</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>中国民主革命的伟大先行者，领导辛亥革命推翻帝制，提出新三民主义与三大政策。</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H88" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>宋庆龄</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr"/>
+      <c r="C89" t="n">
+        <v>1893</v>
+      </c>
+      <c r="D89" t="n">
+        <v>1981</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>中华人民共和国名誉主席，长期致力于妇女儿童与和平事业。</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H89" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>何香凝</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr"/>
+      <c r="C90" t="n">
+        <v>1878</v>
+      </c>
+      <c r="D90" t="n">
+        <v>1972</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>广东南海</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>国民党左派代表人物，中国妇女运动的先驱，曾任全国人大常委会副委员长。</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H90" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>廖仲恺</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr"/>
+      <c r="C91" t="n">
+        <v>1877</v>
+      </c>
+      <c r="D91" t="n">
+        <v>1925</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>广东归善</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>国民党左派领袖，坚定执行联俄、联共、扶助农工三大政策，1925 年在广州遇刺。</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H91" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>张学良</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr"/>
+      <c r="C92" t="n">
+        <v>1901</v>
+      </c>
+      <c r="D92" t="n">
+        <v>2001</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>辽宁台安</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>东北军首领，与杨虎城发动西安事变，促成抗日民族统一战线形成。</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H92" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>杨虎城</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr"/>
+      <c r="C93" t="n">
+        <v>1893</v>
+      </c>
+      <c r="D93" t="n">
+        <v>1949</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>陕西蒲城</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>西北军将领，西安事变发动者之一，1949 年在重庆被杀害。</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H93" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>张澜</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr"/>
+      <c r="C94" t="n">
+        <v>1872</v>
+      </c>
+      <c r="D94" t="n">
+        <v>1955</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>四川南充</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>中国民主同盟主要领导人，曾任中央人民政府副主席。</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H94" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>李济深</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr"/>
+      <c r="C95" t="n">
+        <v>1885</v>
+      </c>
+      <c r="D95" t="n">
+        <v>1959</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>广西苍梧</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>中国国民党革命委员会主要创建人，曾任中央人民政府副主席。</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H95" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>黄炎培</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr"/>
+      <c r="C96" t="n">
+        <v>1878</v>
+      </c>
+      <c r="D96" t="n">
+        <v>1965</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>上海川沙</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>著名教育家，中国民主建国会主要创建人，延安「窑洞对」的对话者。</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H96" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>陈嘉庚</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr"/>
+      <c r="C97" t="n">
+        <v>1874</v>
+      </c>
+      <c r="D97" t="n">
+        <v>1961</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>福建同安</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>爱国华侨领袖，创办集美学校与厦门大学，抗战期间组织南侨机工回国服务。</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H97" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>沈钧儒</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr"/>
+      <c r="C98" t="n">
+        <v>1875</v>
+      </c>
+      <c r="D98" t="n">
+        <v>1963</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>浙江嘉兴</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>救国会「七君子」之首，新中国首任最高人民法院院长。</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H98" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>马叙伦</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr"/>
+      <c r="C99" t="n">
+        <v>1885</v>
+      </c>
+      <c r="D99" t="n">
+        <v>1970</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>浙江杭州</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>中国民主促进会主要创建人，新中国首任教育部部长。</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H99" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>傅作义</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr"/>
+      <c r="C100" t="n">
+        <v>1895</v>
+      </c>
+      <c r="D100" t="n">
+        <v>1974</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>山西荣河</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>国民党将领，率部接受和平改编促成北平和平解放，后任水利部部长。</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H100" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>程潜</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr"/>
+      <c r="C101" t="n">
+        <v>1882</v>
+      </c>
+      <c r="D101" t="n">
+        <v>1968</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>湖南醴陵</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>国民党将领，与陈明仁一同领导湖南和平起义。</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H101" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>茅盾</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>沈雁冰</t>
+        </is>
+      </c>
+      <c r="C102" t="n">
+        <v>1896</v>
+      </c>
+      <c r="D102" t="n">
+        <v>1981</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>浙江桐乡</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>作家，新中国首任文化部部长。</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H102" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>鲁迅</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>周树人</t>
+        </is>
+      </c>
+      <c r="C103" t="n">
+        <v>1881</v>
+      </c>
+      <c r="D103" t="n">
+        <v>1936</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>浙江绍兴</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>文学家、思想家，中国新文化运动的主将。</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H103" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>柳亚子</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr"/>
+      <c r="C104" t="n">
+        <v>1887</v>
+      </c>
+      <c r="D104" t="n">
+        <v>1958</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>江苏吴江</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>爱国诗人，南社创始人之一，与毛泽东有诗词唱和。</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H104" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>郭沫若</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr"/>
+      <c r="C105" t="n">
+        <v>1892</v>
+      </c>
+      <c r="D105" t="n">
+        <v>1978</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>四川乐山</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>作家、历史学家，中国科学院首任院长。</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H105" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>钱学森</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr"/>
+      <c r="C106" t="n">
+        <v>1911</v>
+      </c>
+      <c r="D106" t="n">
+        <v>2009</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>浙江杭州</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>空气动力学家，中国航天事业的奠基人，「两弹一星」功勋奖章获得者。</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H106" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>邓稼先</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr"/>
+      <c r="C107" t="n">
+        <v>1924</v>
+      </c>
+      <c r="D107" t="n">
+        <v>1986</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>安徽怀宁</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>核物理学家，中国原子弹与氢弹研制的主要组织者之一，「两弹一星」功勋奖章获得者。</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H107" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>钱三强</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr"/>
+      <c r="C108" t="n">
+        <v>1913</v>
+      </c>
+      <c r="D108" t="n">
+        <v>1992</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>浙江湖州</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>核物理学家，中国原子能事业的主要开拓者，「两弹一星」功勋奖章获得者。</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H108" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>李四光</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr"/>
+      <c r="C109" t="n">
+        <v>1889</v>
+      </c>
+      <c r="D109" t="n">
+        <v>1971</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>湖北黄冈</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>地质学家，中国地质力学的创立者，为新中国石油勘探作出重大贡献。</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H109" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>袁隆平</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr"/>
+      <c r="C110" t="n">
+        <v>1930</v>
+      </c>
+      <c r="D110" t="n">
+        <v>2021</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>北京</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>杂交水稻研究的开创者，被誉为「杂交水稻之父」，共和国勋章获得者。</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H110" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>屠呦呦</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr"/>
+      <c r="C111" t="n">
+        <v>1930</v>
+      </c>
+      <c r="D111" t="inlineStr"/>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>浙江宁波</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>药学家，发现青蒿素，共和国勋章获得者、诺贝尔生理学或医学奖获得者。</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H111" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>钟南山</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr"/>
+      <c r="C112" t="n">
+        <v>1936</v>
+      </c>
+      <c r="D112" t="inlineStr"/>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>江苏南京</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>呼吸病学专家，在抗击非典和新冠肺炎疫情中作出重大贡献，共和国勋章获得者。</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H112" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>于敏</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr"/>
+      <c r="C113" t="n">
+        <v>1926</v>
+      </c>
+      <c r="D113" t="n">
+        <v>2019</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>天津宁河</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>核物理学家，中国氢弹研制的关键人物，共和国勋章获得者。</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H113" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>孙家栋</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr"/>
+      <c r="C114" t="n">
+        <v>1929</v>
+      </c>
+      <c r="D114" t="inlineStr"/>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>辽宁复县</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>航天技术专家，中国人造卫星与北斗导航工程的重要开创者，共和国勋章获得者。</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H114" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>黄旭华</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr"/>
+      <c r="C115" t="n">
+        <v>1926</v>
+      </c>
+      <c r="D115" t="n">
+        <v>2025</v>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>广东汕尾</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>核潜艇专家，中国第一代核潜艇总设计师，共和国勋章获得者。</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H115" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>张富清</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr"/>
+      <c r="C116" t="n">
+        <v>1924</v>
+      </c>
+      <c r="D116" t="inlineStr"/>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>陕西洋县</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>战斗英雄，转业后深藏功名扎根基层数十年，共和国勋章获得者。</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H116" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>王继才</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr"/>
+      <c r="C117" t="n">
+        <v>1960</v>
+      </c>
+      <c r="D117" t="n">
+        <v>2018</v>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>江苏灌云</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>守岛民兵，与妻子在开山岛守岛 32 年，时代楷模。</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H117" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>黄文秀</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr"/>
+      <c r="C118" t="n">
+        <v>1989</v>
+      </c>
+      <c r="D118" t="n">
+        <v>2019</v>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>广西田阳</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>驻村第一书记，在脱贫攻坚一线因公殉职，时代楷模。</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H118" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>廖俊波</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr"/>
+      <c r="C119" t="n">
+        <v>1968</v>
+      </c>
+      <c r="D119" t="n">
+        <v>2017</v>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>福建浦城</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>福建南平市委常委、副市长，因公殉职，时代楷模。</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H119" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>杨善洲</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr"/>
+      <c r="C120" t="n">
+        <v>1927</v>
+      </c>
+      <c r="D120" t="n">
+        <v>2010</v>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>云南施甸</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>云南保山地委书记，退休后植树造林二十余年并将林场无偿移交国家。</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H120" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>邹碧华</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr"/>
+      <c r="C121" t="n">
+        <v>1967</v>
+      </c>
+      <c r="D121" t="n">
+        <v>2014</v>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>江西奉新</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>上海市高级人民法院副院长，司法体制改革的实干家。</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H121" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>马克思</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>卡尔·马克思</t>
+        </is>
+      </c>
+      <c r="C122" t="n">
+        <v>1818</v>
+      </c>
+      <c r="D122" t="n">
+        <v>1883</v>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>德国特里尔</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>马克思主义的创始人，《共产党宣言》《资本论》的作者。</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H122" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>恩格斯</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>弗里德里希·恩格斯</t>
+        </is>
+      </c>
+      <c r="C123" t="n">
+        <v>1820</v>
+      </c>
+      <c r="D123" t="n">
+        <v>1895</v>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>德国巴门</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>马克思主义的创始人之一，与马克思共同创立科学社会主义。</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H123" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>列宁</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>弗拉基米尔·列宁</t>
+        </is>
+      </c>
+      <c r="C124" t="n">
+        <v>1870</v>
+      </c>
+      <c r="D124" t="n">
+        <v>1924</v>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>俄国辛比尔斯克</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>列宁主义的创立者，领导十月革命建立世界上第一个社会主义国家。</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H124" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>斯大林</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>约瑟夫·斯大林</t>
+        </is>
+      </c>
+      <c r="C125" t="n">
+        <v>1878</v>
+      </c>
+      <c r="D125" t="n">
+        <v>1953</v>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>格鲁吉亚哥里</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>苏联主要领导人，领导苏联卫国战争。</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H125" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>张闻天</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>洛甫</t>
+        </is>
+      </c>
+      <c r="C126" t="n">
+        <v>1900</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1976</v>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>上海南汇</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>遵义会议后接替博古在中央负总责，长期从事党的理论与外交工作。</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H126" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>王稼祥</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr"/>
+      <c r="C127" t="n">
+        <v>1906</v>
+      </c>
+      <c r="D127" t="n">
+        <v>1974</v>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>安徽泾县</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>遵义会议上支持毛泽东的正确主张，新中国首任驻苏联大使，曾任中共中央对外联络部部长。</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H127" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>张国焘</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr"/>
+      <c r="C128" t="n">
+        <v>1897</v>
+      </c>
+      <c r="D128" t="n">
+        <v>1979</v>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>江西萍乡</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>中共一大代表，红四方面军主要领导人，长征中另立中央，1938 年叛党。</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H128" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>项英</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr"/>
+      <c r="C129" t="n">
+        <v>1898</v>
+      </c>
+      <c r="D129" t="n">
+        <v>1941</v>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>湖北武昌</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>中共早期工人运动领导人，新四军副军长兼政治委员，皖南事变中遇害。</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H129" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>李立三</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr"/>
+      <c r="C130" t="n">
+        <v>1899</v>
+      </c>
+      <c r="D130" t="n">
+        <v>1967</v>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>湖南醴陵</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>安源路矿工人大罢工领导人之一，1930 年犯过“左”倾冒险错误。</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H130" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>王明</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>陈绍禹</t>
+        </is>
+      </c>
+      <c r="C131" t="n">
+        <v>1904</v>
+      </c>
+      <c r="D131" t="n">
+        <v>1974</v>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>安徽金寨</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>土地革命战争时期“左”倾教条主义错误的主要代表，抗战初期又犯右倾错误。</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H131" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>博古</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>秦邦宪</t>
+        </is>
+      </c>
+      <c r="C132" t="n">
+        <v>1907</v>
+      </c>
+      <c r="D132" t="n">
+        <v>1946</v>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>江苏无锡</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>中共临时中央主要负责人，遵义会议后仍任中央领导职务，1946 年“四八”空难遇难。</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H132" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>谭震林</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr"/>
+      <c r="C133" t="n">
+        <v>1902</v>
+      </c>
+      <c r="D133" t="n">
+        <v>1983</v>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>湖南攸县</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>井冈山革命根据地创建者之一，曾任国务院副总理、全国人大常委会副委员长。</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H133" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>李富春</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr"/>
+      <c r="C134" t="n">
+        <v>1900</v>
+      </c>
+      <c r="D134" t="n">
+        <v>1975</v>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>湖南长沙</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>曾任国家计划委员会主任、国务院副总理，新中国经济建设的重要组织者。</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H134" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>陆定一</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr"/>
+      <c r="C135" t="n">
+        <v>1906</v>
+      </c>
+      <c r="D135" t="n">
+        <v>1996</v>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>江苏无锡</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>长期主管党的宣传工作，曾任中共中央宣传部部长。</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H135" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>胡乔木</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr"/>
+      <c r="C136" t="n">
+        <v>1912</v>
+      </c>
+      <c r="D136" t="n">
+        <v>1992</v>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>江苏盐城</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>党的重要文献起草人，曾任中国社会科学院院长。</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H136" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>苏兆征</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr"/>
+      <c r="C137" t="n">
+        <v>1885</v>
+      </c>
+      <c r="D137" t="n">
+        <v>1929</v>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>广东香山</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>省港大罢工领导人之一，中华全国总工会首任委员长。</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H137" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>萧楚女</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr"/>
+      <c r="C138" t="n">
+        <v>1893</v>
+      </c>
+      <c r="D138" t="n">
+        <v>1927</v>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>湖北汉阳</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>中共早期青年运动活动家与理论宣传家，1927 年在广州就义。</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H138" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>罗亦农</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr"/>
+      <c r="C139" t="n">
+        <v>1902</v>
+      </c>
+      <c r="D139" t="n">
+        <v>1928</v>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>湖南湘潭</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>上海工人三次武装起义领导人之一，1928 年在上海就义。</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H139" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>邓发</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr"/>
+      <c r="C140" t="n">
+        <v>1906</v>
+      </c>
+      <c r="D140" t="n">
+        <v>1946</v>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>广东云浮</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>中共工人运动领导人，1946 年“四八”空难遇难。</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H140" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>赵博生</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr"/>
+      <c r="C141" t="n">
+        <v>1897</v>
+      </c>
+      <c r="D141" t="n">
+        <v>1933</v>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>河北黄骅</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>宁都起义主要领导人之一，1933 年在江西南城作战牺牲。</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H141" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>董振堂</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr"/>
+      <c r="C142" t="n">
+        <v>1895</v>
+      </c>
+      <c r="D142" t="n">
+        <v>1937</v>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>河北新河</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>宁都起义主要领导人之一，红五军军长，1937 年在甘肃高台牺牲。</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H142" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>黄公略</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr"/>
+      <c r="C143" t="n">
+        <v>1898</v>
+      </c>
+      <c r="D143" t="n">
+        <v>1931</v>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>湖南湘乡</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>红三军军长，中央苏区反“围剿”的主要指挥员之一，1931 年牺牲。</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H143" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>高君宇</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr"/>
+      <c r="C144" t="n">
+        <v>1896</v>
+      </c>
+      <c r="D144" t="n">
+        <v>1925</v>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>山西静乐</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>中共早期青年运动领导人，北京社会主义青年团的创建者之一。</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H144" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>林祥谦</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr"/>
+      <c r="C145" t="n">
+        <v>1892</v>
+      </c>
+      <c r="D145" t="n">
+        <v>1923</v>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>福建闽侯</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>京汉铁路总罢工中江岸分工会委员长，被军阀杀害。</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H145" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>施洋</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr"/>
+      <c r="C146" t="n">
+        <v>1889</v>
+      </c>
+      <c r="D146" t="n">
+        <v>1923</v>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>湖北竹山</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>京汉铁路总罢工的法律顾问，被军阀杀害的“劳工律师”。</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H146" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>顾正红</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr"/>
+      <c r="C147" t="n">
+        <v>1905</v>
+      </c>
+      <c r="D147" t="n">
+        <v>1925</v>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>江苏滨海</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>上海内外棉纱厂工人，1925 年被日本资本家枪杀，成为五卅运动的直接导火线。</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H147" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>刘胡兰</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr"/>
+      <c r="C148" t="n">
+        <v>1932</v>
+      </c>
+      <c r="D148" t="n">
+        <v>1947</v>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>山西文水</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>革命烈士，毛泽东为其题词“生的伟大，死的光荣”。</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H148" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>张思德</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr"/>
+      <c r="C149" t="n">
+        <v>1915</v>
+      </c>
+      <c r="D149" t="n">
+        <v>1944</v>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>四川仪陇</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>中央警备团战士，因公殉职，毛泽东为其作《为人民服务》的演讲。</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H149" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>蔡畅</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr"/>
+      <c r="C150" t="n">
+        <v>1900</v>
+      </c>
+      <c r="D150" t="n">
+        <v>1990</v>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>湖南湘乡</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>中国妇女运动的先驱与领导人，曾任全国妇联主席。</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H150" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>康克清</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr"/>
+      <c r="C151" t="n">
+        <v>1911</v>
+      </c>
+      <c r="D151" t="n">
+        <v>1992</v>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>江西万安</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>妇女儿童事业的领导人，曾任全国妇联主席、全国政协副主席。</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H151" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>习仲勋</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr"/>
+      <c r="C152" t="n">
+        <v>1913</v>
+      </c>
+      <c r="D152" t="n">
+        <v>2002</v>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>陕西富平</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>陕甘边革命根据地创建者之一，曾任国务院副总理、广东省委第一书记。</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H152" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>薄一波</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr"/>
+      <c r="C153" t="n">
+        <v>1908</v>
+      </c>
+      <c r="D153" t="n">
+        <v>2007</v>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>山西定襄</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>曾任国务院副总理、中共中央顾问委员会常务副主任。</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H153" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>万里</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr"/>
+      <c r="C154" t="n">
+        <v>1916</v>
+      </c>
+      <c r="D154" t="n">
+        <v>2015</v>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>山东东平</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>推动安徽农村改革的主要领导人，曾任国务院副总理、全国人大常委会委员长。</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H154" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>谷牧</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr"/>
+      <c r="C155" t="n">
+        <v>1914</v>
+      </c>
+      <c r="D155" t="n">
+        <v>2009</v>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>山东荣成</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>对外开放与经济特区创办的重要组织者，曾任国务院副总理。</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H155" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>姚依林</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr"/>
+      <c r="C156" t="n">
+        <v>1917</v>
+      </c>
+      <c r="D156" t="n">
+        <v>1994</v>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>安徽贵池</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>曾任国务院副总理，长期从事经济工作。</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H156" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>乔石</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr"/>
+      <c r="C157" t="n">
+        <v>1924</v>
+      </c>
+      <c r="D157" t="n">
+        <v>2015</v>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>曾任中共中央纪律检查委员会书记、全国人大常委会委员长。</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H157" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>尉健行</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr"/>
+      <c r="C158" t="n">
+        <v>1931</v>
+      </c>
+      <c r="D158" t="n">
+        <v>2015</v>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>浙江新昌</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>曾任中共中央纪律检查委员会书记。</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H158" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>李瑞环</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr"/>
+      <c r="C159" t="n">
+        <v>1934</v>
+      </c>
+      <c r="D159" t="inlineStr"/>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>天津宝坻</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>曾任全国政协主席。</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H159" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>贾庆林</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr"/>
+      <c r="C160" t="n">
+        <v>1940</v>
+      </c>
+      <c r="D160" t="inlineStr"/>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>河北泊头</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>曾任全国政协主席。</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H160" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>华罗庚</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr"/>
+      <c r="C161" t="n">
+        <v>1910</v>
+      </c>
+      <c r="D161" t="n">
+        <v>1985</v>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>江苏金坛</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>数学家，中国解析数论与多复变函数论研究的开创者。</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H161" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>陈景润</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr"/>
+      <c r="C162" t="n">
+        <v>1933</v>
+      </c>
+      <c r="D162" t="n">
+        <v>1996</v>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>福建福州</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>数学家，在哥德巴赫猜想研究上取得世界领先成果。</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H162" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>周培源</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr"/>
+      <c r="C163" t="n">
+        <v>1902</v>
+      </c>
+      <c r="D163" t="n">
+        <v>1993</v>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>江苏宜兴</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>理论物理学家与流体力学家，曾任北京大学校长。</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H163" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>王淦昌</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr"/>
+      <c r="C164" t="n">
+        <v>1907</v>
+      </c>
+      <c r="D164" t="n">
+        <v>1998</v>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>江苏常熟</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>核物理学家，“两弹一星”功勋奖章获得者。</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H164" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>王大珩</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr"/>
+      <c r="C165" t="n">
+        <v>1915</v>
+      </c>
+      <c r="D165" t="n">
+        <v>2011</v>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>江苏吴县</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>光学专家，“两弹一星”功勋奖章获得者，“863”计划倡议者之一。</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H165" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>陈芳允</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr"/>
+      <c r="C166" t="n">
+        <v>1916</v>
+      </c>
+      <c r="D166" t="n">
+        <v>2000</v>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>浙江黄岩</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>无线电电子学家，“两弹一星”功勋奖章获得者，“863”计划倡议者之一。</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H166" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>杨嘉墀</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr"/>
+      <c r="C167" t="n">
+        <v>1919</v>
+      </c>
+      <c r="D167" t="n">
+        <v>2006</v>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>江苏吴江</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>自动控制专家，“两弹一星”功勋奖章获得者，“863”计划倡议者之一。</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H167" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>郭永怀</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr"/>
+      <c r="C168" t="n">
+        <v>1909</v>
+      </c>
+      <c r="D168" t="n">
+        <v>1968</v>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>山东荣成</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>力学家，“两弹一星”功勋奖章获得者中唯一的烈士。</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H168" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>蒋筑英</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr"/>
+      <c r="C169" t="n">
+        <v>1938</v>
+      </c>
+      <c r="D169" t="n">
+        <v>1982</v>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>浙江杭州</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>光学科学家，知识分子的优秀代表，积劳成疾早逝。</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H169" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>关向应</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr"/>
+      <c r="C170" t="n">
+        <v>1902</v>
+      </c>
+      <c r="D170" t="n">
+        <v>1946</v>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>辽宁金县</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>红二方面军政治委员，八路军第一二〇师政治委员。</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H170" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>李德</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>奥托·布劳恩</t>
+        </is>
+      </c>
+      <c r="C171" t="n">
+        <v>1900</v>
+      </c>
+      <c r="D171" t="n">
+        <v>1974</v>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>德国慕尼黑</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>共产国际派驻中共中央的军事顾问，长征初期军事指挥失误的主要责任人之一。</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H171" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>蒋介石</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr"/>
+      <c r="C172" t="n">
+        <v>1887</v>
+      </c>
+      <c r="D172" t="n">
+        <v>1975</v>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>浙江奉化</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>中国国民党领导人，发动四一二反革命政变，抗战期间任中国战区最高统帅。</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H172" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>汪精卫</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr"/>
+      <c r="C173" t="n">
+        <v>1883</v>
+      </c>
+      <c r="D173" t="n">
+        <v>1944</v>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>广东番禺</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>国民党领导人之一，抗日战争期间公开投敌，在南京成立伪国民政府。</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H173" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>阎锡山</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr"/>
+      <c r="C174" t="n">
+        <v>1883</v>
+      </c>
+      <c r="D174" t="n">
+        <v>1960</v>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>山西五台</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>晋系军阀首领，抗战初期与八路军在山西有过合作。</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H174" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>何应钦</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr"/>
+      <c r="C175" t="n">
+        <v>1890</v>
+      </c>
+      <c r="D175" t="n">
+        <v>1987</v>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>贵州兴义</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>国民党军政要员，1945 年代表中国战区接受日本投降。</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H175" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>张治中</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr"/>
+      <c r="C176" t="n">
+        <v>1890</v>
+      </c>
+      <c r="D176" t="n">
+        <v>1969</v>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>安徽巢县</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>国民党将领，1949 年国共北平和谈国民党方面首席代表，后留在北平参加新中国建设。</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H176" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
